--- a/artfynd/A 47036-2025 artfynd.xlsx
+++ b/artfynd/A 47036-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2059464</v>
+        <v>415623</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597766.0286032234</v>
+        <v>597612</v>
       </c>
       <c r="R2" t="n">
-        <v>7154665.888307604</v>
+        <v>7154863</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2012-09-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>blandsumpskog</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -782,7 +767,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # brandstubbe av tall</t>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -803,12 +788,7 @@
         <v>1564301</v>
       </c>
       <c r="B3" t="n">
-        <v>89611</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597579.9457114921</v>
+        <v>597580</v>
       </c>
       <c r="R3" t="n">
-        <v>7154760.391309706</v>
+        <v>7154760</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +853,9 @@
           <t>2012-09-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>415623</v>
+        <v>2059464</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597611.6228752328</v>
+        <v>597766</v>
       </c>
       <c r="R4" t="n">
-        <v>7154863.163764865</v>
+        <v>7154666</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,19 +963,9 @@
           <t>2012-09-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-09-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +979,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>blandsumpskog</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1032,7 +987,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>1 substratenheter # brandstubbe av tall</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
